--- a/Database/edopro-rush-card-ids.xlsx
+++ b/Database/edopro-rush-card-ids.xlsx
@@ -4122,7 +4122,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>執念の竜</t>
+          <t>竜の執念</t>
         </is>
       </c>
     </row>
@@ -5482,7 +5482,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>アサルト・アルマート</t>
+          <t>アサルト・キャノン・ビートル</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>背番号９９ 球児皇龍ホームグランドラ</t>
+          <t>デュエリスト</t>
         </is>
       </c>
     </row>
@@ -6553,7 +6553,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>背番号３９ 球児皇ホーム</t>
+          <t>デュエリスト</t>
         </is>
       </c>
     </row>
@@ -7471,7 +7471,7 @@
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Ｃ背番号３９ 球児皇ホームプレート</t>
+          <t>デュエリスト</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>デュエルマーカー</t>
+          <t>蒼救天使 ソレイル</t>
         </is>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
       </c>
       <c r="C706" t="inlineStr">
         <is>
-          <t>デュエルマーカー</t>
+          <t>蒼救天使 ルーア</t>
         </is>
       </c>
     </row>
@@ -16175,7 +16175,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>デュエルマーカー</t>
+          <t>蒼救の願い</t>
         </is>
       </c>
     </row>
@@ -30880,7 +30880,7 @@
       </c>
       <c r="C1814" t="inlineStr">
         <is>
-          <t>フュージョン・ゲート</t>
+          <t>フュージョン</t>
         </is>
       </c>
     </row>
@@ -33379,7 +33379,7 @@
       </c>
       <c r="C1961" t="inlineStr">
         <is>
-          <t>ハーピィ・レディ三姉妹</t>
+          <t>ハーピィ三姉妹</t>
         </is>
       </c>
     </row>
@@ -36269,7 +36269,7 @@
       </c>
       <c r="C2131" t="inlineStr">
         <is>
-          <t>永久磁石の戦士α</t>
+          <t>磁石の戦士α</t>
         </is>
       </c>
     </row>
@@ -36286,7 +36286,7 @@
       </c>
       <c r="C2132" t="inlineStr">
         <is>
-          <t>永久磁石の戦士β</t>
+          <t>磁石の戦士β</t>
         </is>
       </c>
     </row>
@@ -36303,7 +36303,7 @@
       </c>
       <c r="C2133" t="inlineStr">
         <is>
-          <t>永久磁石の戦士γ</t>
+          <t>磁石の戦士γ</t>
         </is>
       </c>
     </row>
@@ -37663,7 +37663,7 @@
       </c>
       <c r="C2213" t="inlineStr">
         <is>
-          <t>はじまりの星域</t>
+          <t>はじまりの星</t>
         </is>
       </c>
     </row>
@@ -42644,7 +42644,7 @@
       </c>
       <c r="C2506" t="inlineStr">
         <is>
-          <t>Ｃ背番号３９ 球児皇ホームプレートＶ</t>
+          <t>デュエリスト</t>
         </is>
       </c>
     </row>
